--- a/output/2026-08-31_22_Italia_Liguria_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-08-31_22_Italia_Liguria_Depolverazione_Trattamento_aria.xlsx
@@ -489,8 +489,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Studio di ingegneria specializzato in progettazione impianti di abbattimento polveri, depolverazione e mitigazione odori industriali (dust, biofiltri, scrubber, post-combustori). Coerente col target come partner tecnico-prescrittivo piu' che rivenditore diretto. Contatti non confermati da fonte affidabile.</t>
@@ -528,7 +526,6 @@
           <t>010 566193</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Daikin Comfort Store dal 1984. Attivita' principale climatizzazione civile/commerciale; offre anche ventilazione meccanica e aspirazione per clienti industriali. Componente industriale non predominante, da qualificare ulteriormente.</t>
@@ -603,11 +600,9 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vendita, noleggio, assistenza aspiratori industriali (linea BIEMMEDUE, modelli MT/MTV/QT/Q-BAT/TH), deumidificatori, generatori aria calda, idropulitrici. Forte coerenza col target.</t>
+          <t>Vendita, noleggio, assistenza aspiratori industriali (linea BIEMMEDUE, modelli MT/MTV/QT/Q-BAT/TH), deumidificatori, generatori aria calda, idropulitrici. Forte coerenza col target. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
